--- a/result/morris/morris_first_inf_ONLY_Signed_N512_seed2024.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N512_seed2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,97 +453,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.95952690972219</v>
+        <v>-17.66780598958333</v>
       </c>
       <c r="C2" t="n">
-        <v>32.87293836805554</v>
+        <v>24.19786241319446</v>
       </c>
       <c r="D2" t="n">
-        <v>24.73411749705838</v>
+        <v>29.52661848675406</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-23.13384331597223</v>
+        <v>19.47233072916663</v>
       </c>
       <c r="C3" t="n">
-        <v>26.85432942708335</v>
+        <v>22.32530381944443</v>
       </c>
       <c r="D3" t="n">
-        <v>28.86284369053115</v>
+        <v>21.13391682518399</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.43712022569447</v>
+        <v>13.40163845486113</v>
       </c>
       <c r="C4" t="n">
-        <v>25.70600043402778</v>
+        <v>19.71565755208331</v>
       </c>
       <c r="D4" t="n">
-        <v>28.22342873986483</v>
+        <v>29.60572925034297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.06092664930554</v>
+        <v>10.12754991319445</v>
       </c>
       <c r="C5" t="n">
-        <v>20.73204210069443</v>
+        <v>17.67106119791666</v>
       </c>
       <c r="D5" t="n">
-        <v>24.92483142175559</v>
+        <v>22.8900028942447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3121202256944444</v>
+        <v>7.33485243055556</v>
       </c>
       <c r="C6" t="n">
-        <v>7.356499565972222</v>
+        <v>12.34288194444445</v>
       </c>
       <c r="D6" t="n">
-        <v>16.48134237333862</v>
+        <v>20.71847028269563</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.618218315972223</v>
+        <v>-3.533203125000001</v>
       </c>
       <c r="C7" t="n">
-        <v>4.535644531249999</v>
+        <v>10.09809027777778</v>
       </c>
       <c r="D7" t="n">
-        <v>10.36329783456781</v>
+        <v>18.11487089364263</v>
       </c>
     </row>
     <row r="8">
@@ -553,93 +553,109 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.350802951388889</v>
+        <v>-1.575249565972222</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5859375</v>
+        <v>7.102593315972225</v>
       </c>
       <c r="D8" t="n">
-        <v>10.60211230358423</v>
+        <v>16.76832606120412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.640896267361121</v>
+        <v>-1.709798177083333</v>
       </c>
       <c r="C9" t="n">
-        <v>2.929524739583347</v>
+        <v>6.731499565972227</v>
       </c>
       <c r="D9" t="n">
-        <v>3.412799933612482</v>
+        <v>15.70230430353891</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.501573350694446</v>
+        <v>-1.30419921875</v>
       </c>
       <c r="C10" t="n">
-        <v>2.536512586805557</v>
+        <v>3.713270399305558</v>
       </c>
       <c r="D10" t="n">
-        <v>8.344528552849397</v>
+        <v>10.75642914492075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.310926649305555</v>
+        <v>2.792805989583343</v>
       </c>
       <c r="C11" t="n">
-        <v>2.10888671875</v>
+        <v>2.792805989583343</v>
       </c>
       <c r="D11" t="n">
-        <v>5.646988931833671</v>
+        <v>0.3473078578283298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.008138020833333</v>
+        <v>0.5908745659722221</v>
       </c>
       <c r="C12" t="n">
-        <v>1.988498263888889</v>
+        <v>2.161946614583333</v>
       </c>
       <c r="D12" t="n">
-        <v>10.95010852670365</v>
+        <v>8.088187654904567</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.098198784722222</v>
+        <v>0.7726779513888888</v>
       </c>
       <c r="C13" t="n">
-        <v>1.846788194444444</v>
+        <v>1.884548611111112</v>
       </c>
       <c r="D13" t="n">
-        <v>9.59648850554478</v>
+        <v>8.507097431490196</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8681640625</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.752061631944444</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.381482820881389</v>
       </c>
     </row>
   </sheetData>
